--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_11.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0322919154100836</v>
+        <v>0.02797450398376614</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008460085995390417</v>
+        <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>46904786</v>
+        <v>3973575</v>
       </c>
       <c r="L2" t="n">
-        <v>23927495</v>
+        <v>1700445</v>
       </c>
       <c r="M2" t="n">
-        <v>5330131</v>
+        <v>301556</v>
       </c>
       <c r="N2" t="n">
-        <v>231834</v>
+        <v>6584</v>
       </c>
       <c r="O2" t="n">
-        <v>3198930</v>
+        <v>184752</v>
       </c>
       <c r="P2" t="n">
-        <v>1204260</v>
+        <v>448</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999858736991882</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8117715716362</v>
+        <v>0.7212334275245667</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6610845923423767</v>
+        <v>0.5308442711830139</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5791991353034973</v>
+        <v>0.4035938084125519</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1916308104991913</v>
+        <v>0.04461399838328362</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6299643516540527</v>
+        <v>0.4007331430912018</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7569630146026611</v>
+        <v>0.4076433181762695</v>
       </c>
       <c r="X2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69993891</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53175479</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33163018</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8850920</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>652300</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5064045</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982621</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9557910561561584</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116975665092468</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578632473945618</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6612526774406433</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019046425819397</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314442276954651</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008555133192305178</v>
+        <v>0.00725865420768453</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00202627677219498</v>
+        <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>46904786</v>
+        <v>3973575</v>
       </c>
       <c r="E3" t="n">
-        <v>8283204</v>
+        <v>965306</v>
       </c>
       <c r="F3" t="n">
-        <v>290683</v>
+        <v>41537</v>
       </c>
       <c r="G3" t="n">
-        <v>35470</v>
+        <v>4301</v>
       </c>
       <c r="H3" t="n">
-        <v>22588</v>
+        <v>3952</v>
       </c>
       <c r="I3" t="n">
-        <v>1496</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>111056319</v>
+        <v>10069588</v>
       </c>
       <c r="K3" t="n">
-        <v>114636903</v>
+        <v>9891445</v>
       </c>
       <c r="L3" t="n">
-        <v>132331028</v>
+        <v>11573255</v>
       </c>
       <c r="M3" t="n">
-        <v>166848858</v>
+        <v>15025996</v>
       </c>
       <c r="N3" t="n">
-        <v>179085765</v>
+        <v>16184900</v>
       </c>
       <c r="O3" t="n">
-        <v>173553236</v>
+        <v>15627139</v>
       </c>
       <c r="P3" t="n">
-        <v>178535218</v>
+        <v>16221417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8445482850074768</v>
+        <v>0.7965129017829895</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6563864350318909</v>
+        <v>0.5091295838356018</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5159913301467896</v>
+        <v>0.3193153738975525</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2347747832536697</v>
+        <v>0.07306868582963943</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5693119764328003</v>
+        <v>0.3604368567466736</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5655576586723328</v>
+        <v>0.002310088137164712</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53175479</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2192163</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>94407</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75574</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>111057309</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>123053320</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141385832</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>169254833</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179729565</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174881471</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178775944</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9574558138847351</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097381830215454</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8568266034126282</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6605743765830994</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012455940246582</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311000108718872</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07137920743998651</v>
+        <v>0.06323345159809228</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03198645682554076</v>
+        <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>9987929</v>
+        <v>1372088</v>
       </c>
       <c r="E4" t="n">
-        <v>23927495</v>
+        <v>1700445</v>
       </c>
       <c r="F4" t="n">
-        <v>2091512</v>
+        <v>207011</v>
       </c>
       <c r="G4" t="n">
-        <v>160272</v>
+        <v>23351</v>
       </c>
       <c r="H4" t="n">
-        <v>260648</v>
+        <v>36857</v>
       </c>
       <c r="I4" t="n">
-        <v>25418</v>
+        <v>142</v>
       </c>
       <c r="J4" t="n">
-        <v>990</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>10875985</v>
+        <v>1535841</v>
       </c>
       <c r="L4" t="n">
-        <v>12266806</v>
+        <v>1502839</v>
       </c>
       <c r="M4" t="n">
-        <v>3872457</v>
+        <v>445621</v>
       </c>
       <c r="N4" t="n">
-        <v>977961</v>
+        <v>140993</v>
       </c>
       <c r="O4" t="n">
-        <v>1879024</v>
+        <v>276283</v>
       </c>
       <c r="P4" t="n">
-        <v>386650</v>
+        <v>651</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999929070472717</v>
+        <v>0.9999974370002747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8278356790542603</v>
+        <v>0.7570062279701233</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6587271690368652</v>
+        <v>0.5197602510452271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5457712411880493</v>
+        <v>0.3565418720245361</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2110201269388199</v>
+        <v>0.05540129169821739</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5981044173240662</v>
+        <v>0.3795183598995209</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6474094390869141</v>
+        <v>0.004594141617417336</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2297185</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33163018</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>918333</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61374</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12703</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>753</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2459568</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3212002</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1466482</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>334161</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>550789</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145924</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566227197647095</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107168316841125</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8573446273803711</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.660913348197937</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9015750288963318</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931272029876709</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>639745</v>
+        <v>121629</v>
       </c>
       <c r="E5" t="n">
-        <v>3167256</v>
+        <v>399774</v>
       </c>
       <c r="F5" t="n">
-        <v>5330131</v>
+        <v>301556</v>
       </c>
       <c r="G5" t="n">
-        <v>307812</v>
+        <v>37765</v>
       </c>
       <c r="H5" t="n">
-        <v>800275</v>
+        <v>83495</v>
       </c>
       <c r="I5" t="n">
-        <v>84524</v>
+        <v>161</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8633526</v>
+        <v>1015139</v>
       </c>
       <c r="L5" t="n">
-        <v>12525871</v>
+        <v>1639461</v>
       </c>
       <c r="M5" t="n">
-        <v>4999754</v>
+        <v>642827</v>
       </c>
       <c r="N5" t="n">
-        <v>755640</v>
+        <v>83523</v>
       </c>
       <c r="O5" t="n">
-        <v>2420010</v>
+        <v>327826</v>
       </c>
       <c r="P5" t="n">
-        <v>925072</v>
+        <v>193484</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999945163726807</v>
+        <v>0.9999980330467224</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8922431468963623</v>
+        <v>0.8446040153503418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8630626201629639</v>
+        <v>0.8085830807685852</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9509961009025574</v>
+        <v>0.933695912361145</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9904248118400574</v>
+        <v>0.986323356628418</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9762551188468933</v>
+        <v>0.9631999731063843</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9927549958229065</v>
+        <v>0.9881740212440491</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89547</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>950629</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8850920</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>110142</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321676</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6971</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2362833</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3290348</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1478965</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>335174</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>554895</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146711</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733644127845764</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964085578918457</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837313890457153</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963030815124512</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938929677009583</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983837008476257</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>172961</v>
+        <v>22802</v>
       </c>
       <c r="E6" t="n">
-        <v>225472</v>
+        <v>27293</v>
       </c>
       <c r="F6" t="n">
-        <v>237924</v>
+        <v>24570</v>
       </c>
       <c r="G6" t="n">
-        <v>231834</v>
+        <v>6584</v>
       </c>
       <c r="H6" t="n">
-        <v>106619</v>
+        <v>8775</v>
       </c>
       <c r="I6" t="n">
-        <v>12534</v>
+        <v>77</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>72280</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59401</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>121076</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>652300</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77120</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5297</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>261</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>70371</v>
+        <v>17882</v>
       </c>
       <c r="E7" t="n">
-        <v>534974</v>
+        <v>98555</v>
       </c>
       <c r="F7" t="n">
-        <v>1139024</v>
+        <v>149513</v>
       </c>
       <c r="G7" t="n">
-        <v>412702</v>
+        <v>61640</v>
       </c>
       <c r="H7" t="n">
-        <v>3198930</v>
+        <v>184752</v>
       </c>
       <c r="I7" t="n">
-        <v>262678</v>
+        <v>235</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>248</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8917</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>329015</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>84142</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5064045</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132573</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4979</v>
+        <v>1440</v>
       </c>
       <c r="E8" t="n">
-        <v>55900</v>
+        <v>11911</v>
       </c>
       <c r="F8" t="n">
-        <v>113314</v>
+        <v>22990</v>
       </c>
       <c r="G8" t="n">
-        <v>61705</v>
+        <v>13936</v>
       </c>
       <c r="H8" t="n">
-        <v>688894</v>
+        <v>143204</v>
       </c>
       <c r="I8" t="n">
-        <v>1204260</v>
+        <v>448</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>892</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3651</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2929</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138931</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982621</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
